--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>995</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>4.154835129878475</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>36</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.6569681739980209</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>982</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>4.100550851799662</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>35</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.6387190580536314</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1070</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>4.46801365725625</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>52</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.9489540291082524</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>1026</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>4.284282254527956</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>37</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.6752172899424104</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>1066</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>4.451310802462769</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>36</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.6569681739980209</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>1115</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>4.655920773682915</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>55</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.003701376941421</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>1146</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>4.785367898332396</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>51</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.9307049131638628</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>1084</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>4.526473649033435</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>41</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.7482137537199682</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>1068</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>4.45966222985951</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>42</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.7664628696643576</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>1167</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>4.873057885998172</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>43</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.7847119856087472</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>1238</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>5.169533558582466</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>38</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.6934664058867999</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>1169</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>4.881409313394913</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>39</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.7117155218311892</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>1175</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>4.829436033256606</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>50</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.9098404521979834</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>1265</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>5.199350282612431</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>50</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.9098404521979834</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>1311</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>5.38841756561652</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>51</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.9280372612419431</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>1210</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>4.973291574672761</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>37</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.6732819346265078</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>1270</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>5.21990107424331</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>38</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.6914787436704675</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>1231</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>5.059604899522453</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>55</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.000824497417782</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>1234</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>5.07193537450098</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>39</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.7096755527144272</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>1387</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>5.700789598405883</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>46</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.8370532160221449</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>1197</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>4.919859516432474</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>34</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.6186915074946288</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>1267</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>5.207570599264783</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>39</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.7096755527144272</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>1366</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>5.614476273556191</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>47</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.8552500250661046</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>1229</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>5.051384582870101</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>33</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.6004946984506691</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>1342</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>5.426379486651966</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>30</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.5446231534551983</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>1256</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>5.078638327298711</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>32</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.5809313636855448</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>1360</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>5.499162520004973</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>41</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.7443183097221042</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>1094</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>4.423591027121647</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>39</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.7080100994917576</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>1387</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>5.608337070034483</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>43</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.7806265199524507</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>1325</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>5.357639955151904</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>24</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.4356985227641586</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>1293</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>5.228247895857669</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>45</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.8169347301827973</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>1361</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>5.503206021857918</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>66</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.198170937601436</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>1286</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>5.199943382887055</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>29</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.5264690483400249</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>1428</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>5.774120646005222</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>45</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.8169347301827973</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>1372</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>5.547684542240311</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>46</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.8350888352979705</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>766</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>3.097322419355742</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>35</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.6353936790310646</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>1158</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>4.609926656982503</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>56</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.015276926299869</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>1069</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>4.255623140167786</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>45</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.8158475300623951</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>752</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>2.993665670164804</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>26</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.4713785729249395</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>1136</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>4.522346012376618</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>42</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.7614576947249021</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>1176</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>4.681583548023681</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>41</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.7433277496124044</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>764</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>3.041436930858923</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>30</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.5438983533749301</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>1242</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>4.944325481841338</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>27</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.4895085180374371</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>1259</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>5.01200143449134</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>43</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.7795876398373999</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>817</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>3.252426665591283</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>33</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.5982881887124231</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>1301</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>5.179200846920756</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>43</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.7795876398373999</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>1263</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>5.027925188056046</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>36</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.6526780240499162</v>
       </c>
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>896</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>3.566920798494234</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>32</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.5801582435999254</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>1285</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>5.042633998874688</v>
       </c>
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>35</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.6338559868331812</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>1176</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>4.614893060448741</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>29</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.5251949605189216</v>
       </c>
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>1286</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>5.046558227667587</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>35</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.6338559868331812</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>1206</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>4.732619924235699</v>
       </c>
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>49</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.8873983815664538</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>1334</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>5.234921209726719</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>54</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.9779492368283368</v>
       </c>
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>1119</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>4.391212019253522</v>
       </c>
@@ -43137,9 +42816,6 @@
       <c r="O216" t="n">
         <v>32</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.5795254736760515</v>
       </c>
@@ -43533,9 +43209,6 @@
       <c r="O218" t="n">
         <v>961</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>3.771183869975545</v>
       </c>
@@ -43929,9 +43602,6 @@
       <c r="O220" t="n">
         <v>39</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.7062966710426877</v>
       </c>
@@ -44325,9 +43995,6 @@
       <c r="O222" t="n">
         <v>991</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>3.888910733762503</v>
       </c>
@@ -44721,9 +44388,6 @@
       <c r="O224" t="n">
         <v>48</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.8692882105140772</v>
       </c>
@@ -45117,9 +44781,6 @@
       <c r="O226" t="n">
         <v>951</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>3.731941582046559</v>
       </c>
@@ -45513,9 +45174,6 @@
       <c r="O228" t="n">
         <v>37</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.6700763289379345</v>
       </c>
@@ -45909,9 +45567,6 @@
       <c r="O230" t="n">
         <v>978</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>3.837895759454821</v>
       </c>
@@ -46305,9 +45960,6 @@
       <c r="O232" t="n">
         <v>36</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.6519661578855579</v>
       </c>
@@ -46701,9 +46353,6 @@
       <c r="O234" t="n">
         <v>851</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>3.3395187027567</v>
       </c>
@@ -47097,9 +46746,6 @@
       <c r="O236" t="n">
         <v>42</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.7606271841998176</v>
       </c>
@@ -47493,9 +47139,6 @@
       <c r="O238" t="n">
         <v>926</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>3.633835862224094</v>
       </c>
@@ -47888,9 +47531,6 @@
       </c>
       <c r="O240" t="n">
         <v>40</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0.7244068420950643</v>

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40311,7 +40311,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41097,7 +41097,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41883,7 +41883,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45027,7 +45027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47385,7 +47385,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
